--- a/docs/d/209/inyear.xlsx
+++ b/docs/d/209/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 95 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 94 clubs short</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10774,19 +10774,19 @@
         <v>2</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U104" s="9" t="n">
-        <v>0</v>
+      <c r="U104" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V104" s="9" t="n">
         <v>0</v>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15553,8 +15553,8 @@
       <c r="Y153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="9" t="n">
-        <v>0</v>
+      <c r="Z153" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA153" s="10" t="n">
         <v>1</v>
@@ -17860,7 +17860,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -18190,7 +18190,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/d/209/inyear.xlsx
+++ b/docs/d/209/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/209/inyear.xlsx
+++ b/docs/d/209/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 15 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 15 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 94 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 90 clubs short</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6532,8 +6532,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>0</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6823,8 +6823,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9539,8 +9539,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12934,8 +12934,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -16882,7 +16882,7 @@
         </is>
       </c>
       <c r="P167" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q167" s="9" t="n">
         <v>0</v>
@@ -16897,7 +16897,7 @@
         <v>1</v>
       </c>
       <c r="U167" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V167" s="9" t="n">
         <v>0</v>
@@ -17563,7 +17563,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -17596,7 +17596,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -17794,7 +17794,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -18025,7 +18025,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/209/inyear.xlsx
+++ b/docs/d/209/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 15 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 15 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 90 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 60 clubs short</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1003,8 +1003,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1585,8 +1585,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2652,8 +2652,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3137,8 +3137,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3525,8 +3525,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4177,8 +4177,8 @@
       <c r="P36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" s="9" t="n">
-        <v>1</v>
+      <c r="Q36" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4786,8 +4786,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6144,8 +6144,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="9" t="n">
         <v>0</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6338,8 +6338,8 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7114,8 +7114,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7599,8 +7599,8 @@
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7696,8 +7696,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8860,8 +8860,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8957,8 +8957,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>0</v>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>1</v>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="10" t="n">
         <v>2</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9830,8 +9830,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10412,8 +10412,8 @@
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10882,8 +10882,8 @@
       <c r="T105" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U105" s="9" t="n">
-        <v>0</v>
+      <c r="U105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V105" s="10" t="n">
         <v>4</v>
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11188,8 +11188,8 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11285,8 +11285,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11479,8 +11479,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11576,8 +11576,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -11770,8 +11770,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="9" t="n">
         <v>0</v>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11964,8 +11964,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>0</v>
@@ -12914,13 +12914,13 @@
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U126" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V126" s="9" t="n">
         <v>2</v>
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13002,7 +13002,7 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q127" s="9" t="n">
         <v>0</v>
@@ -13031,8 +13031,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13128,8 +13128,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13419,8 +13419,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13584,10 +13584,10 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q133" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13789,8 +13789,8 @@
       <c r="S135" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T135" s="9" t="n">
-        <v>0</v>
+      <c r="T135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U135" s="9" t="n">
         <v>0</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13904,8 +13904,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14098,8 +14098,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14389,8 +14389,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14486,8 +14486,8 @@
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15650,8 +15650,8 @@
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -16647,7 +16647,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -16717,8 +16717,8 @@
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
@@ -17200,7 +17200,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -17233,7 +17233,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -17299,7 +17299,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -17332,7 +17332,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -17365,7 +17365,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -17398,7 +17398,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -17464,7 +17464,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -17563,7 +17563,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -17596,7 +17596,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -17629,7 +17629,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -17662,7 +17662,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -17728,7 +17728,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17794,7 +17794,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17860,7 +17860,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -17893,7 +17893,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17926,7 +17926,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17959,7 +17959,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -18025,7 +18025,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -18058,7 +18058,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -18091,7 +18091,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -18124,7 +18124,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -18223,7 +18223,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -18289,7 +18289,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/209/inyear.xlsx
+++ b/docs/d/209/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 15 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 15 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 60 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 60 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1723,17 +1723,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2208,17 +2208,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2343,8 +2343,8 @@
       <c r="S17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
+      <c r="T17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U17" s="9" t="n">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3275,17 +3275,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4439,17 +4439,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4536,17 +4536,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5215,17 +5215,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M47" s="8" t="n">
@@ -5259,11 +5259,11 @@
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="9" t="n">
-        <v>1</v>
+      <c r="V47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W47" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>6</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5506,17 +5506,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M50" s="8" t="n">
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6029,8 +6029,8 @@
       <c r="S55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T55" s="9" t="n">
-        <v>0</v>
+      <c r="T55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U55" s="9" t="n">
         <v>0</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6476,17 +6476,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X69" s="10" t="n">
         <v>6</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>2</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
@@ -7737,17 +7737,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8319,17 +8319,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8348,8 +8348,8 @@
       <c r="P79" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" s="9" t="n">
-        <v>1</v>
+      <c r="Q79" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
@@ -8367,7 +8367,7 @@
         <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>7</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="P85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q85" s="9" t="n">
         <v>1</v>
@@ -8998,17 +8998,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9046,7 +9046,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>5</v>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9192,17 +9192,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9386,17 +9386,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9483,17 +9483,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -9519,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="S91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" s="9" t="n">
         <v>0</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="X92" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -9722,7 +9722,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97" s="10" t="n">
         <v>1</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>79</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10779,8 +10779,8 @@
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S104" s="9" t="n">
-        <v>1</v>
+      <c r="S104" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T104" s="10" t="n">
         <v>1</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>2</v>
       </c>
       <c r="R105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S105" s="10" t="n">
         <v>4</v>
@@ -10889,7 +10889,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>7</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>4</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11467,8 +11467,8 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>3</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -11952,14 +11952,14 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>0</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="9" t="n">
-        <v>0</v>
+      <c r="X116" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12049,11 +12049,11 @@
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="9" t="n">
-        <v>2</v>
+      <c r="V117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X117" s="10" t="n">
         <v>6</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12140,8 +12140,8 @@
       <c r="S118" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T118" s="9" t="n">
-        <v>0</v>
+      <c r="T118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U118" s="9" t="n">
         <v>0</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12443,8 +12443,8 @@
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X121" s="9" t="n">
-        <v>0</v>
+      <c r="X121" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -12490,17 +12490,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -12520,7 +12520,7 @@
         <v>2</v>
       </c>
       <c r="Q122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -12632,13 +12632,13 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="9" t="n">
-        <v>0</v>
+      <c r="X123" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>0</v>
@@ -12825,8 +12825,8 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>2</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12920,13 +12920,13 @@
         <v>1</v>
       </c>
       <c r="U126" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W126" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="V126" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W126" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>6</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -13196,28 +13196,28 @@
         </is>
       </c>
       <c r="P129" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W129" s="9" t="n">
-        <v>0</v>
+      <c r="W129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X129" s="10" t="n">
         <v>7</v>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -13595,8 +13595,8 @@
       <c r="S133" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="T133" s="9" t="n">
-        <v>0</v>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -13795,8 +13795,8 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>3</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -13893,7 +13893,7 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -13990,7 +13990,7 @@
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14236,17 +14236,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L140" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -14527,17 +14527,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -14572,7 +14572,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -14915,17 +14915,17 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L147" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M147" s="8" t="n">
@@ -14960,7 +14960,7 @@
         <v>2</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="S150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T150" s="9" t="n">
         <v>0</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -15497,17 +15497,17 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L153" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M153" s="8" t="n">
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15594,13 +15594,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -15638,8 +15638,8 @@
       <c r="U154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V154" s="9" t="n">
-        <v>1</v>
+      <c r="V154" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
@@ -15982,13 +15982,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="V164" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W164" s="9" t="n">
         <v>0</v>
@@ -16706,7 +16706,7 @@
         <v>0</v>
       </c>
       <c r="V165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -16855,13 +16855,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
@@ -16905,8 +16905,8 @@
       <c r="W167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X167" s="9" t="n">
-        <v>3</v>
+      <c r="X167" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y167" s="9" t="n">
         <v>0</v>
@@ -16952,17 +16952,17 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L168" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M168" s="8" t="n">
@@ -16997,7 +16997,7 @@
         <v>0</v>
       </c>
       <c r="V168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -17266,7 +17266,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -17281,7 +17281,7 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -17380,7 +17380,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -17446,7 +17446,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -17497,7 +17497,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -17530,7 +17530,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -17578,7 +17578,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -17677,7 +17677,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -17695,13 +17695,13 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -17710,7 +17710,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -17743,7 +17743,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -17809,7 +17809,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -17860,7 +17860,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -17926,7 +17926,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17959,7 +17959,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -18007,7 +18007,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -18025,7 +18025,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -18058,13 +18058,13 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -18091,7 +18091,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -18172,7 +18172,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -18205,7 +18205,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -18223,7 +18223,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -18304,7 +18304,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/209/inyear.xlsx
+++ b/docs/d/209/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/209/inyear.xlsx
+++ b/docs/d/209/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/209/inyear.xlsx
+++ b/docs/d/209/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/209/inyear.xlsx
+++ b/docs/d/209/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/209/inyear.xlsx
+++ b/docs/d/209/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 15 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 15 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 60 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 60 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3319,11 +3319,11 @@
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="9" t="n">
-        <v>0</v>
+      <c r="V27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X27" s="9" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-21</v>
+        <v>-10</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>4</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8319,17 +8319,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L79" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8366,8 +8366,8 @@
       <c r="V79" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W79" s="9" t="n">
-        <v>3</v>
+      <c r="W79" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>7</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9036,8 +9036,8 @@
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
@@ -9386,17 +9386,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L90" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9434,7 +9434,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>4</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-19</v>
+        <v>-17</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q96" s="9" t="n">
         <v>1</v>
@@ -10009,11 +10009,11 @@
       <c r="T96" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" s="9" t="n">
+      <c r="U96" s="10" t="n">
         <v>2</v>
+      </c>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10976,11 +10976,11 @@
       <c r="S106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" s="9" t="n">
-        <v>0</v>
+      <c r="T106" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V106" s="9" t="n">
         <v>1</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>2</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13107,8 +13107,8 @@
       <c r="R128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S128" s="9" t="n">
-        <v>0</v>
+      <c r="S128" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T128" s="10" t="n">
         <v>1</v>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13198,8 +13198,8 @@
       <c r="P129" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Q129" s="9" t="n">
-        <v>0</v>
+      <c r="Q129" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R129" s="9" t="n">
         <v>0</v>
@@ -13584,7 +13584,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q133" s="10" t="n">
         <v>2</v>
@@ -14957,7 +14957,7 @@
         <v>1</v>
       </c>
       <c r="U147" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V147" s="9" t="n">
         <v>2</v>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -15594,13 +15594,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>4</v>
       </c>
       <c r="W154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X154" s="10" t="n">
         <v>4</v>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -17710,7 +17710,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -17728,7 +17728,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -17827,7 +17827,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17893,7 +17893,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -18025,13 +18025,13 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>

--- a/docs/d/209/inyear.xlsx
+++ b/docs/d/209/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 15 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 15 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 60 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 60 clubs short</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1758,8 +1758,8 @@
       <c r="R11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="9" t="n">
-        <v>0</v>
+      <c r="S11" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T11" s="9" t="n">
         <v>0</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="9" t="n">
         <v>0</v>
@@ -3025,8 +3025,8 @@
       <c r="T24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U24" s="9" t="n">
-        <v>0</v>
+      <c r="U24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V24" s="9" t="n">
         <v>0</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="P31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="10" t="n">
         <v>2</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5738,8 +5738,8 @@
       <c r="S52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T52" s="9" t="n">
-        <v>0</v>
+      <c r="T52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U52" s="9" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="P57" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q57" s="9" t="n">
         <v>0</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7737,17 +7737,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="L73" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -7972,8 +7972,8 @@
       <c r="T75" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U75" s="9" t="n">
-        <v>0</v>
+      <c r="U75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V75" s="9" t="n">
         <v>2</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>1</v>
@@ -10068,10 +10068,10 @@
         <v>24</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -10873,8 +10873,8 @@
       <c r="Q105" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R105" s="9" t="n">
-        <v>1</v>
+      <c r="R105" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S105" s="10" t="n">
         <v>4</v>
@@ -10889,7 +10889,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>7</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>4</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12784,10 +12784,10 @@
         <v>16</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>6</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13204,8 +13204,8 @@
       <c r="R129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S129" s="9" t="n">
-        <v>0</v>
+      <c r="S129" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T129" s="9" t="n">
         <v>0</v>
@@ -13463,10 +13463,10 @@
         <v>9</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -15444,11 +15444,11 @@
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="9" t="n">
-        <v>3</v>
+      <c r="V152" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X152" s="10" t="n">
         <v>5</v>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -17332,7 +17332,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -17530,7 +17530,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -17662,7 +17662,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -17677,7 +17677,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -17860,7 +17860,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -18025,7 +18025,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -18190,7 +18190,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
